--- a/excelTemplate/EmptyStock.xlsx
+++ b/excelTemplate/EmptyStock.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11028"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\git\zt\zhongtan-server\excelTemplate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/liudong/workspace/xiangmeng/git/zhongtan/zhongtan-server/excelTemplate/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{495B8C9E-48DC-A94C-84F9-6E30A889FC89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28005" windowHeight="11745"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="28000" windowHeight="11740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17,14 +18,14 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$1</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="50">
   <si>
     <t>S/N</t>
   </si>
@@ -458,7 +459,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>empty_stock_depot_name</t>
+      <t>empty_stock_storing_days</t>
     </r>
     <r>
       <rPr>
@@ -485,7 +486,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>empty_stock_storing_days</t>
+      <t>empty_stock_detention_days</t>
     </r>
     <r>
       <rPr>
@@ -501,18 +502,7 @@
   </si>
   <si>
     <r>
-      <t>&lt;%=rs1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>empty_stock_detention_days</t>
+      <t>&lt;%=rs1.empty_stock_depot_name</t>
     </r>
     <r>
       <rPr>
@@ -524,14 +514,22 @@
       </rPr>
       <t>%&gt;</t>
     </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Terminal Name</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;%=rs1.empty_stock_terminal_name%&gt;</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="9" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -645,32 +643,29 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -685,39 +680,27 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal 3" xfId="1"/>
+    <cellStyle name="Normal 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -734,9 +717,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -774,9 +757,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -811,7 +794,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -846,7 +829,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1019,109 +1002,113 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="9" style="19"/>
-    <col min="2" max="2" width="23.875" style="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="17.625" style="19" customWidth="1"/>
-    <col min="5" max="5" width="18.375" style="19" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.375" style="19" customWidth="1"/>
-    <col min="7" max="7" width="26.25" style="19" customWidth="1"/>
-    <col min="8" max="8" width="23.875" style="19" customWidth="1"/>
-    <col min="9" max="9" width="24.375" style="19" customWidth="1"/>
-    <col min="10" max="10" width="23.625" style="19" customWidth="1"/>
-    <col min="11" max="11" width="25" style="19" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.625" style="19" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="29.375" style="19" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="19"/>
+    <col min="2" max="2" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="17.6640625" customWidth="1"/>
+    <col min="5" max="5" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.33203125" customWidth="1"/>
+    <col min="7" max="7" width="26.1640625" customWidth="1"/>
+    <col min="8" max="8" width="23.83203125" customWidth="1"/>
+    <col min="9" max="10" width="24.33203125" customWidth="1"/>
+    <col min="11" max="11" width="23.6640625" customWidth="1"/>
+    <col min="12" max="12" width="25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="29.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" ht="47.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="47" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="L1" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="M1" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="20" t="s">
+      <c r="N1" s="12" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A2" s="19" t="s">
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="K2" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="L2" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="M2" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="L2" s="21" t="s">
+      <c r="N2" s="17" t="s">
         <v>46</v>
-      </c>
-      <c r="M2" s="22" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M1"/>
+  <autoFilter ref="A1:N1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1129,16 +1116,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:W1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="5" max="5" width="6.375" customWidth="1"/>
-    <col min="13" max="13" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="10.1640625" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" customWidth="1"/>
+    <col min="13" max="13" width="6.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="1" customFormat="1" ht="47.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:23" s="1" customFormat="1" ht="47" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1160,52 +1147,52 @@
       <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="N1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="O1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="P1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="10" t="s">
+      <c r="Q1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="10" t="s">
+      <c r="R1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="10" t="s">
+      <c r="S1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="10" t="s">
+      <c r="T1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="12" t="s">
+      <c r="U1" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="12" t="s">
+      <c r="V1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="9" t="s">
+      <c r="W1" s="8" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1217,9 +1204,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
